--- a/output/top_partidas_bp_2026S1_vs_2025S1.xlsx
+++ b/output/top_partidas_bp_2026S1_vs_2025S1.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -494,33 +494,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Participación (%) = x_t / X_t. Con signos mixtos puede ser negativa o superar 100%; por eso el ranking de participación ordena por participación absoluta |x_t| / Σ|x_t|.</t>
+          <t>Participación (%) = x_t / X_t: peso de la partida sobre el SALDO NETO de la cuenta. Si hay partidas de signo contrario que se compensan, el neto es pequeño y la participación puede ser negativa o superar 100% (las participaciones suman 100%, pero mezclando positivos y negativos).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Crecimiento (%) = (x_t − x_b) / |x_b|. Con saldos negativos, crecimiento positivo = el saldo sube (p. ej. menor déficit / menor salida neta).</t>
+          <t>Peso bruto (%) = |x_t| / Σ|x_t|: tamaño de la partida sobre la suma de los valores absolutos de todas las partidas (siempre entre 0 y 100%, suman 100%). El ranking de participación se ordena por esta medida. Peso bruto = |participación| × |X_t| / Σ|x_t|, así que la razón entre ambas es la misma para todas las partidas de una tabla.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ranking de crecimiento: solo partidas con participación absoluta ≥ 1.0% en t o en b, para evitar crecimientos enormes de partidas con base casi nula.</t>
+          <t>Crecimiento (%) = (x_t − x_b) / |x_b|. Con saldos negativos, crecimiento positivo = el saldo sube (p. ej. menor déficit / menor salida neta).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Contribución (p.p.) = (x_t − x_b) / |X_b|; la suma de contribuciones es el crecimiento del total. Ranking por valor absoluto (el signo indica si empuja hacia arriba o hacia abajo).</t>
+          <t>Ranking de crecimiento: solo partidas con peso bruto ≥ 1.0% en t o en b, para evitar crecimientos enormes de partidas con base casi nula.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>Contribución (p.p.) = (x_t − x_b) / |X_b|; la suma de contribuciones es el crecimiento del total. Ranking por valor absoluto (el signo indica si empuja hacia arriba o hacia abajo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Hoja 'Control': total oficial BanRep vs suma de partidas (debe ser ≈ 0).</t>
         </is>
@@ -537,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -549,6 +556,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,7 +603,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -605,15 +613,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -643,12 +656,15 @@
         <v>-34.60018920043832</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>-71.94695506152118</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>-11549.338209</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>-8580.47695</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>-2968.861258999999</v>
       </c>
     </row>
@@ -676,12 +692,15 @@
         <v>3.955845997378684</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>5.969646670177607</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>6473.4478279</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>6227.1128341</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>246.3349937999992</v>
       </c>
     </row>
@@ -709,12 +728,15 @@
         <v>99.28489274057381</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>45.13286634093851</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>3738.1920229</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>1875.80301321</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>1862.38900969</v>
       </c>
     </row>
@@ -742,12 +764,15 @@
         <v>10.77992165520008</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>7.34155371559685</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>-2507.335563</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>-2810.281732</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>302.9461689999998</v>
       </c>
     </row>
@@ -775,19 +800,22 @@
         <v>-4.217866802055251</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>-1.944841629388017</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>1822.4405517</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1902.69363487</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>-80.25308317000008</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -819,20 +847,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -862,12 +895,15 @@
         <v>8.847805050242822</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>45.13286634093851</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>3738.1920229</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>1875.80301321</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>1862.38900969</v>
       </c>
     </row>
@@ -895,12 +931,15 @@
         <v>2.144662742428269</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>4.563702839891798</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>906.1186486399999</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>717.79934385</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>188.3193047899999</v>
       </c>
     </row>
@@ -928,12 +967,15 @@
         <v>1.404727089245956</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>2.190288616777919</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>-593.4963044</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>-683.8776557</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>90.38135130000001</v>
       </c>
     </row>
@@ -961,12 +1003,15 @@
         <v>5.934530950005797</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>7.34155371559685</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>-2507.335563</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>-2810.281732</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>302.9461689999998</v>
       </c>
     </row>
@@ -994,12 +1039,15 @@
         <v>1.080892947804232</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>1.222010591452984</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>-456.676585</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>-507.1023452</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>50.42576019999996</v>
       </c>
     </row>
@@ -1233,7 +1281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1245,6 +1293,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1291,7 +1340,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1301,15 +1350,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -1339,12 +1393,15 @@
         <v>6.601121069276347</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>3.179246588005677</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>24606.131911</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>23082.43259</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>1523.699321</v>
       </c>
     </row>
@@ -1372,12 +1429,15 @@
         <v>4.196805991119714</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>0.5611413286401138</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>6677.0223433</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>6408.0873495</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>268.9349938000005</v>
       </c>
     </row>
@@ -1405,12 +1465,15 @@
         <v>4.710937406274398</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>0.4451489510800211</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>4742.0390741</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>4528.6950834</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>213.3439907000002</v>
       </c>
     </row>
@@ -1438,12 +1501,15 @@
         <v>99.28489274057381</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>3.885933282893551</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>3738.1920229</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1875.80301321</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>1862.38900969</v>
       </c>
     </row>
@@ -1471,19 +1537,22 @@
         <v>-2.83049254141773</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>-0.1127289906327372</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>1854.72132359</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>1908.74830191</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>-54.02697832000013</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -1515,20 +1584,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -1558,12 +1632,15 @@
         <v>7.07275688144669</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>3.885933282893551</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>3738.1920229</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>1875.80301321</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>1862.38900969</v>
       </c>
     </row>
@@ -1591,12 +1668,15 @@
         <v>2.178634224439142</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>0.4351307482030462</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>1151.48211866</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>942.93949473</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>208.54262393</v>
       </c>
     </row>
@@ -1624,12 +1704,15 @@
         <v>1.126044594448911</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>0.1773821663312405</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>595.15278002</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>510.13984412</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>85.0129359</v>
       </c>
     </row>
@@ -1657,12 +1740,15 @@
         <v>2.888437343847148</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>0.4251496469019899</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>1526.63715414</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>1322.87811552</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>203.75903862</v>
       </c>
     </row>
@@ -1690,12 +1776,15 @@
         <v>1.661742103528221</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>0.2436840052121575</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>878.28709224</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>761.49805339</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>116.78903885</v>
       </c>
     </row>
@@ -1929,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1941,6 +2030,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1987,7 +2077,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1997,15 +2087,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -2035,12 +2130,15 @@
         <v>14.18871684651883</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>8.630761704719442</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>36155.47012</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>31662.90954</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>4492.560579999998</v>
       </c>
     </row>
@@ -2068,12 +2166,15 @@
         <v>-8.86776726408724</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>-0.5710726978463021</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>3054.8784719</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>3352.1382942</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>-297.2598223</v>
       </c>
     </row>
@@ -2101,12 +2202,15 @@
         <v>12.93300249748917</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>0.6581884610494911</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>2991.6900267</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>2649.0839352</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>342.6060915000003</v>
       </c>
     </row>
@@ -2134,12 +2238,15 @@
         <v>7.658015335100989</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>0.3329421121525017</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>2436.3724738</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>2263.0664946</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>173.3059792000004</v>
       </c>
     </row>
@@ -2167,19 +2274,22 @@
         <v>1.231273968504289</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>0.05172218544567295</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>2213.5110169</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>2186.5881265</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>26.92289040000014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -2211,20 +2321,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -2254,12 +2369,15 @@
         <v>2.999219044021556</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>1.574144638276231</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>1764.5626811</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>945.17496179</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>819.3877193100002</v>
       </c>
     </row>
@@ -2287,12 +2405,15 @@
         <v>1.600500084965264</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>0.5397968199147032</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>941.6393666399999</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>660.6595415300001</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>280.9798251099999</v>
       </c>
     </row>
@@ -2320,12 +2441,15 @@
         <v>61.45328567294514</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>8.630761704719442</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>36155.47012</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>31662.90954</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>4492.560579999998</v>
       </c>
     </row>
@@ -2353,12 +2477,15 @@
         <v>5.084961729041294</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>0.6581884610494911</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>2991.6900267</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>2649.0839352</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>342.6060915000003</v>
       </c>
     </row>
@@ -2386,12 +2513,15 @@
         <v>1.985537298322376</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>0.2515891899005246</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>1168.1724366</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>1037.21300155</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>130.9594350499997</v>
       </c>
     </row>
@@ -2625,7 +2755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2637,6 +2767,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2683,7 +2814,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2693,15 +2824,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -2731,12 +2867,15 @@
         <v>184.4399788027567</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>287.5360452542449</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>4236.602720899999</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>-5017.2948655</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>9253.897586399999</v>
       </c>
     </row>
@@ -2764,12 +2903,15 @@
         <v>-26.68609345759412</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>-25.93195530758279</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>-3961.9738039</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>-3127.3944091</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>-834.5793947999996</v>
       </c>
     </row>
@@ -2797,12 +2939,15 @@
         <v>-23.40720119966143</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>-27.63763370750261</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>2910.5274634</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>3800.0014479</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>-889.4739845000004</v>
       </c>
     </row>
@@ -2830,12 +2975,15 @@
         <v>-7.658015335100989</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>-5.384943523831274</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>-2436.3724738</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>-2263.0664946</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>-173.3059792000004</v>
       </c>
     </row>
@@ -2863,19 +3011,22 @@
         <v>-13.19162264279267</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>-7.609451929476482</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>-2101.3666611</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>-1856.4683605</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>-244.8983005999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -2907,20 +3058,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -2950,12 +3106,15 @@
         <v>3.830895536895315</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>66.95320196487845</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>1414.9036757</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>-739.88033935</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>2154.78401505</v>
       </c>
     </row>
@@ -2983,12 +3142,15 @@
         <v>4.061296471295168</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>34.17907393361526</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -3016,12 +3178,15 @@
         <v>11.47073312044712</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>287.5360452542449</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>4236.602720899999</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>-5017.2948655</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>9253.897586399999</v>
       </c>
     </row>
@@ -3049,12 +3214,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>13.2102120753423</v>
       </c>
       <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>-425.15</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>425.15</v>
       </c>
     </row>
@@ -3082,12 +3250,15 @@
         <v>5.089597675644761</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>26.61054101651739</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>1879.79295957</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>1023.3743458</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>856.4186137700001</v>
       </c>
     </row>
@@ -3321,7 +3492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3333,6 +3504,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3379,7 +3551,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -3389,15 +3561,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -3427,12 +3604,15 @@
         <v>-23.40720119966143</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>-10.87836012815961</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>2910.5274634</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>3800.0014479</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>-889.4739845000004</v>
       </c>
     </row>
@@ -3460,12 +3640,15 @@
         <v>-196.1765508694293</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>-16.29539846606748</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>-2011.5849581</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>-679.1844094999999</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>-1332.4005486</v>
       </c>
     </row>
@@ -3493,12 +3676,15 @@
         <v>83.68576145032384</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>10.4740894769242</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>1879.79295957</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>1023.3743458</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>856.4186137700001</v>
       </c>
     </row>
@@ -3526,12 +3712,15 @@
         <v>15.40270688807229</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>2.49199441479105</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>1526.63715414</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1322.87811552</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>203.75903862</v>
       </c>
     </row>
@@ -3559,19 +3748,22 @@
         <v>-230.4936985458787</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>-12.57380060763012</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>-1474.1460529</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>-446.0436188</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>-1028.1024341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -3603,20 +3795,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -3646,12 +3843,15 @@
         <v>11.41027922051075</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>10.4740894769242</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>1879.79295957</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>1023.3743458</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>856.4186137700001</v>
       </c>
     </row>
@@ -3679,12 +3879,15 @@
         <v>0.4967642904288022</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>0.9964135516554951</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>-81.839716423</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>-163.31191642</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>81.47219999699999</v>
       </c>
     </row>
@@ -3712,12 +3915,15 @@
         <v>9.266635513481207</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>2.49199441479105</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>1526.63715414</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>1322.87811552</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>203.75903862</v>
       </c>
     </row>
@@ -3745,12 +3951,15 @@
         <v>4.910236626278913</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>0.8375488627672355</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>808.93973421</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>740.4571766</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>68.48255760999996</v>
       </c>
     </row>
@@ -3778,12 +3987,15 @@
         <v>6.378927718904231</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>-0.2450974014114981</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>1050.90008613</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>1070.94058485</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>-20.04049871999996</v>
       </c>
     </row>
@@ -4017,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4029,6 +4241,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4075,7 +4288,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4085,15 +4298,20 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -4123,12 +4341,15 @@
         <v>-184.4399788027567</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>-81.2109552059984</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>-4236.602720899999</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>5017.2948655</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>-9253.897586399999</v>
       </c>
     </row>
@@ -4156,12 +4377,15 @@
         <v>26.68609345759412</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>7.324156034162358</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>3961.9738039</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>3127.3944091</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>834.5793947999996</v>
       </c>
     </row>
@@ -4189,12 +4413,15 @@
         <v>7.658015335100989</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>1.520909863366901</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>2436.3724738</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>2263.0664946</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>173.3059792000004</v>
       </c>
     </row>
@@ -4222,12 +4449,15 @@
         <v>13.19162264279267</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>2.149194405315309</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>2101.3666611</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1856.4683605</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>244.8983005999999</v>
       </c>
     </row>
@@ -4255,19 +4485,22 @@
         <v>113.3477111147772</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>8.11029649577563</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>1739.49039415</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>815.33117232</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>924.15922183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Top 5 por crecimiento (partidas con participación abs. ≥ 1.0%)</t>
+          <t>Top 5 por crecimiento (partidas con peso bruto ≥ 1.0%)</t>
         </is>
       </c>
     </row>
@@ -4299,20 +4532,25 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Contribución (p.p.)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
           <t>Valor 2026S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Valor 2025S1 (USD mill.)</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Variación (USD mill.)</t>
         </is>
@@ -4342,12 +4580,15 @@
         <v>1.959070144678479</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>3.066409865314939</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>400.81520586</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>51.40122865</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>349.41397721</v>
       </c>
     </row>
@@ -4375,12 +4616,15 @@
         <v>1.967426922219132</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>4.271613262024385</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>402.52495756</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>-84.22059979999995</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>486.7455573599999</v>
       </c>
     </row>
@@ -4408,12 +4652,15 @@
         <v>1.478983135760117</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>3.881522766848095</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>302.59198816</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>-139.70319323</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>442.2951813899999</v>
       </c>
     </row>
@@ -4441,12 +4688,15 @@
         <v>1.988448870322073</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>10.60475336889841</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>406.82593498</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>-801.5738598</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>1208.39979478</v>
       </c>
     </row>
@@ -4474,12 +4724,15 @@
         <v>0.8323024763076078</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>5.588721007145318</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>170.28460634</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>-466.54390661</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>636.82851295</v>
       </c>
     </row>
@@ -4773,7 +5026,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Participación abs. 2026S1 (%)</t>
+          <t>Peso bruto 2026S1 (%)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
